--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412462</v>
+        <v>122412105</v>
       </c>
       <c r="B2" t="n">
-        <v>105290</v>
+        <v>74686</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713727</v>
+        <v>713555</v>
       </c>
       <c r="R2" t="n">
-        <v>6628747</v>
+        <v>6628671</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412228</v>
+        <v>122412462</v>
       </c>
       <c r="B5" t="n">
         <v>105290</v>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713560</v>
+        <v>713727</v>
       </c>
       <c r="R5" t="n">
-        <v>6628732</v>
+        <v>6628747</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412105</v>
+        <v>122412228</v>
       </c>
       <c r="B6" t="n">
-        <v>74686</v>
+        <v>105290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713555</v>
+        <v>713560</v>
       </c>
       <c r="R6" t="n">
-        <v>6628671</v>
+        <v>6628732</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412105</v>
+        <v>122412260</v>
       </c>
       <c r="B2" t="n">
-        <v>74686</v>
+        <v>105303</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713555</v>
+        <v>713590</v>
       </c>
       <c r="R2" t="n">
-        <v>6628671</v>
+        <v>6628731</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412338</v>
+        <v>122412228</v>
       </c>
       <c r="B3" t="n">
-        <v>8425</v>
+        <v>105303</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713683</v>
+        <v>713560</v>
       </c>
       <c r="R3" t="n">
-        <v>6628738</v>
+        <v>6628732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412260</v>
+        <v>122412105</v>
       </c>
       <c r="B4" t="n">
-        <v>105290</v>
+        <v>74691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713590</v>
+        <v>713555</v>
       </c>
       <c r="R4" t="n">
-        <v>6628731</v>
+        <v>6628671</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>122412462</v>
       </c>
       <c r="B5" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412228</v>
+        <v>122412338</v>
       </c>
       <c r="B6" t="n">
-        <v>105290</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713560</v>
+        <v>713683</v>
       </c>
       <c r="R6" t="n">
-        <v>6628732</v>
+        <v>6628738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412260</v>
+        <v>122412338</v>
       </c>
       <c r="B2" t="n">
-        <v>105303</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713590</v>
+        <v>713683</v>
       </c>
       <c r="R2" t="n">
-        <v>6628731</v>
+        <v>6628738</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412228</v>
+        <v>122412260</v>
       </c>
       <c r="B3" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713560</v>
+        <v>713590</v>
       </c>
       <c r="R3" t="n">
-        <v>6628732</v>
+        <v>6628731</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412462</v>
+        <v>122412228</v>
       </c>
       <c r="B5" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713727</v>
+        <v>713560</v>
       </c>
       <c r="R5" t="n">
-        <v>6628747</v>
+        <v>6628732</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412338</v>
+        <v>122412462</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>105308</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713683</v>
+        <v>713727</v>
       </c>
       <c r="R6" t="n">
-        <v>6628738</v>
+        <v>6628747</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412338</v>
+        <v>122412105</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
+        <v>74692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Björksplintborre</t>
-        </is>
+        <v>6426</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713683</v>
+        <v>713555</v>
       </c>
       <c r="R2" t="n">
-        <v>6628738</v>
+        <v>6628671</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412260</v>
+        <v>122412228</v>
       </c>
       <c r="B3" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -795,11 +790,6 @@
       <c r="E3" t="n">
         <v>221144</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Pyrola chlorantha</t>
@@ -817,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713590</v>
+        <v>713560</v>
       </c>
       <c r="R3" t="n">
-        <v>6628731</v>
+        <v>6628732</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412105</v>
+        <v>122412260</v>
       </c>
       <c r="B4" t="n">
-        <v>74691</v>
+        <v>105317</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +885,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713555</v>
+        <v>713590</v>
       </c>
       <c r="R4" t="n">
-        <v>6628671</v>
+        <v>6628731</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412228</v>
+        <v>122412338</v>
       </c>
       <c r="B5" t="n">
-        <v>105308</v>
+        <v>8430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +982,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>106554</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713560</v>
+        <v>713683</v>
       </c>
       <c r="R5" t="n">
-        <v>6628732</v>
+        <v>6628738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1066,7 @@
         <v>122412462</v>
       </c>
       <c r="B6" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,11 +1080,6 @@
       </c>
       <c r="E6" t="n">
         <v>221144</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412105</v>
+        <v>122412462</v>
       </c>
       <c r="B2" t="n">
-        <v>74692</v>
+        <v>105330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>221144</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713555</v>
+        <v>713727</v>
       </c>
       <c r="R2" t="n">
-        <v>6628671</v>
+        <v>6628747</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412228</v>
+        <v>122412105</v>
       </c>
       <c r="B3" t="n">
-        <v>105317</v>
+        <v>74696</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -788,16 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>6426</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713560</v>
+        <v>713555</v>
       </c>
       <c r="R3" t="n">
-        <v>6628732</v>
+        <v>6628671</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412260</v>
+        <v>122412338</v>
       </c>
       <c r="B4" t="n">
-        <v>105317</v>
+        <v>8430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -885,16 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>106554</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713590</v>
+        <v>713683</v>
       </c>
       <c r="R4" t="n">
-        <v>6628731</v>
+        <v>6628738</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412338</v>
+        <v>122412228</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
+        <v>105330</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -982,16 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713683</v>
+        <v>713560</v>
       </c>
       <c r="R5" t="n">
-        <v>6628738</v>
+        <v>6628732</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412462</v>
+        <v>122412260</v>
       </c>
       <c r="B6" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1081,6 +1101,11 @@
       <c r="E6" t="n">
         <v>221144</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Pyrola chlorantha</t>
@@ -1098,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713727</v>
+        <v>713590</v>
       </c>
       <c r="R6" t="n">
-        <v>6628747</v>
+        <v>6628731</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412462</v>
+        <v>122412338</v>
       </c>
       <c r="B2" t="n">
-        <v>105330</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713727</v>
+        <v>713683</v>
       </c>
       <c r="R2" t="n">
-        <v>6628747</v>
+        <v>6628738</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412338</v>
+        <v>122412462</v>
       </c>
       <c r="B4" t="n">
-        <v>8430</v>
+        <v>105343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713683</v>
+        <v>713727</v>
       </c>
       <c r="R4" t="n">
-        <v>6628738</v>
+        <v>6628747</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412228</v>
+        <v>122412260</v>
       </c>
       <c r="B5" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713560</v>
+        <v>713590</v>
       </c>
       <c r="R5" t="n">
-        <v>6628732</v>
+        <v>6628731</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412260</v>
+        <v>122412228</v>
       </c>
       <c r="B6" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713590</v>
+        <v>713560</v>
       </c>
       <c r="R6" t="n">
-        <v>6628731</v>
+        <v>6628732</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412338</v>
+        <v>122412462</v>
       </c>
       <c r="B2" t="n">
-        <v>8430</v>
+        <v>105343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713683</v>
+        <v>713727</v>
       </c>
       <c r="R2" t="n">
-        <v>6628738</v>
+        <v>6628747</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412105</v>
+        <v>122412260</v>
       </c>
       <c r="B3" t="n">
-        <v>74696</v>
+        <v>105343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713555</v>
+        <v>713590</v>
       </c>
       <c r="R3" t="n">
-        <v>6628671</v>
+        <v>6628731</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412462</v>
+        <v>122412228</v>
       </c>
       <c r="B4" t="n">
         <v>105343</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713727</v>
+        <v>713560</v>
       </c>
       <c r="R4" t="n">
-        <v>6628747</v>
+        <v>6628732</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412260</v>
+        <v>122412105</v>
       </c>
       <c r="B5" t="n">
-        <v>105343</v>
+        <v>74696</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713590</v>
+        <v>713555</v>
       </c>
       <c r="R5" t="n">
-        <v>6628731</v>
+        <v>6628671</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412228</v>
+        <v>122412338</v>
       </c>
       <c r="B6" t="n">
-        <v>105343</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713560</v>
+        <v>713683</v>
       </c>
       <c r="R6" t="n">
-        <v>6628732</v>
+        <v>6628738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412462</v>
+        <v>122412260</v>
       </c>
       <c r="B2" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713727</v>
+        <v>713590</v>
       </c>
       <c r="R2" t="n">
-        <v>6628747</v>
+        <v>6628731</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412260</v>
+        <v>122412105</v>
       </c>
       <c r="B3" t="n">
-        <v>105343</v>
+        <v>74696</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713590</v>
+        <v>713555</v>
       </c>
       <c r="R3" t="n">
-        <v>6628731</v>
+        <v>6628671</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412228</v>
+        <v>122412338</v>
       </c>
       <c r="B4" t="n">
-        <v>105343</v>
+        <v>8430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713560</v>
+        <v>713683</v>
       </c>
       <c r="R4" t="n">
-        <v>6628732</v>
+        <v>6628738</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412105</v>
+        <v>122412228</v>
       </c>
       <c r="B5" t="n">
-        <v>74696</v>
+        <v>105346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713555</v>
+        <v>713560</v>
       </c>
       <c r="R5" t="n">
-        <v>6628671</v>
+        <v>6628732</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412338</v>
+        <v>122412462</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>105346</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713683</v>
+        <v>713727</v>
       </c>
       <c r="R6" t="n">
-        <v>6628738</v>
+        <v>6628747</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412260</v>
+        <v>122412228</v>
       </c>
       <c r="B2" t="n">
         <v>105346</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713590</v>
+        <v>713560</v>
       </c>
       <c r="R2" t="n">
-        <v>6628731</v>
+        <v>6628732</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412105</v>
+        <v>122412260</v>
       </c>
       <c r="B3" t="n">
-        <v>74696</v>
+        <v>105346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713555</v>
+        <v>713590</v>
       </c>
       <c r="R3" t="n">
-        <v>6628671</v>
+        <v>6628731</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412338</v>
+        <v>122412462</v>
       </c>
       <c r="B4" t="n">
-        <v>8430</v>
+        <v>105346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713683</v>
+        <v>713727</v>
       </c>
       <c r="R4" t="n">
-        <v>6628738</v>
+        <v>6628747</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412228</v>
+        <v>122412338</v>
       </c>
       <c r="B5" t="n">
-        <v>105346</v>
+        <v>8430</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713560</v>
+        <v>713683</v>
       </c>
       <c r="R5" t="n">
-        <v>6628732</v>
+        <v>6628738</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412462</v>
+        <v>122412105</v>
       </c>
       <c r="B6" t="n">
-        <v>105346</v>
+        <v>74696</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713727</v>
+        <v>713555</v>
       </c>
       <c r="R6" t="n">
-        <v>6628747</v>
+        <v>6628671</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412228</v>
+        <v>122412462</v>
       </c>
       <c r="B2" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713560</v>
+        <v>713727</v>
       </c>
       <c r="R2" t="n">
-        <v>6628732</v>
+        <v>6628747</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412260</v>
+        <v>122412228</v>
       </c>
       <c r="B3" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713590</v>
+        <v>713560</v>
       </c>
       <c r="R3" t="n">
-        <v>6628731</v>
+        <v>6628732</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412462</v>
+        <v>122412338</v>
       </c>
       <c r="B4" t="n">
-        <v>105346</v>
+        <v>8430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713727</v>
+        <v>713683</v>
       </c>
       <c r="R4" t="n">
-        <v>6628747</v>
+        <v>6628738</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412338</v>
+        <v>122412105</v>
       </c>
       <c r="B5" t="n">
-        <v>8430</v>
+        <v>74697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713683</v>
+        <v>713555</v>
       </c>
       <c r="R5" t="n">
-        <v>6628738</v>
+        <v>6628671</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412105</v>
+        <v>122412260</v>
       </c>
       <c r="B6" t="n">
-        <v>74696</v>
+        <v>105347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713555</v>
+        <v>713590</v>
       </c>
       <c r="R6" t="n">
-        <v>6628671</v>
+        <v>6628731</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412462</v>
+        <v>122412105</v>
       </c>
       <c r="B2" t="n">
-        <v>105347</v>
+        <v>74700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713727</v>
+        <v>713555</v>
       </c>
       <c r="R2" t="n">
-        <v>6628747</v>
+        <v>6628671</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412228</v>
+        <v>122412260</v>
       </c>
       <c r="B3" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713560</v>
+        <v>713590</v>
       </c>
       <c r="R3" t="n">
-        <v>6628732</v>
+        <v>6628731</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412338</v>
+        <v>122412228</v>
       </c>
       <c r="B4" t="n">
-        <v>8430</v>
+        <v>105350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713683</v>
+        <v>713560</v>
       </c>
       <c r="R4" t="n">
-        <v>6628738</v>
+        <v>6628732</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412105</v>
+        <v>122412462</v>
       </c>
       <c r="B5" t="n">
-        <v>74697</v>
+        <v>105350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713555</v>
+        <v>713727</v>
       </c>
       <c r="R5" t="n">
-        <v>6628671</v>
+        <v>6628747</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412260</v>
+        <v>122412338</v>
       </c>
       <c r="B6" t="n">
-        <v>105347</v>
+        <v>8430</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>106554</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713590</v>
+        <v>713683</v>
       </c>
       <c r="R6" t="n">
-        <v>6628731</v>
+        <v>6628738</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 824-2025 artfynd.xlsx
+++ b/artfynd/A 824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122412105</v>
+        <v>122412338</v>
       </c>
       <c r="B2" t="n">
-        <v>74700</v>
+        <v>8430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>713555</v>
+        <v>713683</v>
       </c>
       <c r="R2" t="n">
-        <v>6628671</v>
+        <v>6628738</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122412260</v>
+        <v>122412228</v>
       </c>
       <c r="B3" t="n">
         <v>105350</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>713590</v>
+        <v>713560</v>
       </c>
       <c r="R3" t="n">
-        <v>6628731</v>
+        <v>6628732</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122412228</v>
+        <v>122412462</v>
       </c>
       <c r="B4" t="n">
         <v>105350</v>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>713560</v>
+        <v>713727</v>
       </c>
       <c r="R4" t="n">
-        <v>6628732</v>
+        <v>6628747</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122412462</v>
+        <v>122412105</v>
       </c>
       <c r="B5" t="n">
-        <v>105350</v>
+        <v>74700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>713727</v>
+        <v>713555</v>
       </c>
       <c r="R5" t="n">
-        <v>6628747</v>
+        <v>6628671</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122412338</v>
+        <v>122412260</v>
       </c>
       <c r="B6" t="n">
-        <v>8430</v>
+        <v>105350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106554</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>713683</v>
+        <v>713590</v>
       </c>
       <c r="R6" t="n">
-        <v>6628738</v>
+        <v>6628731</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
